--- a/Config/Excels/__tables__.xlsx
+++ b/Config/Excels/__tables__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="228"/>
+    <workbookView windowWidth="7305" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -108,6 +108,72 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>Tables.TbAudio</t>
+  </si>
+  <si>
+    <t>AudioConfig</t>
+  </si>
+  <si>
+    <t>.\Tables\Audio_audio.xlsx</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>Tables.TbMap</t>
+  </si>
+  <si>
+    <t>MapConfig</t>
+  </si>
+  <si>
+    <t>.\Tables\Map_map.xlsx</t>
+  </si>
+  <si>
+    <t>Tables.TbModel</t>
+  </si>
+  <si>
+    <t>ModelConfig</t>
+  </si>
+  <si>
+    <t>.\Tables\Model_model.xlsx</t>
+  </si>
+  <si>
+    <t>Tables.Global</t>
+  </si>
+  <si>
+    <t>GlobalConfig</t>
+  </si>
+  <si>
+    <t>.\Tables\Global_global.xlsx</t>
+  </si>
+  <si>
+    <t>singleton</t>
+  </si>
+  <si>
+    <t>Tables.TbBadWords</t>
+  </si>
+  <si>
+    <t>BadWordsConfig</t>
+  </si>
+  <si>
+    <t>.\Tables\Words_BadWords.xlsx</t>
+  </si>
+  <si>
+    <t>list</t>
+  </si>
+  <si>
+    <t>Tables.TbNpc</t>
+  </si>
+  <si>
+    <t>NpcConfig</t>
+  </si>
+  <si>
+    <t>.\Tables\Npc_npc.xlsx</t>
+  </si>
+  <si>
+    <t>、</t>
   </si>
 </sst>
 </file>
@@ -120,7 +186,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,6 +197,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -608,151 +681,148 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1073,121 +1143,216 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="38.75" customWidth="1"/>
-    <col min="3" max="3" width="23.5583333333333" customWidth="1"/>
-    <col min="4" max="4" width="32.425" customWidth="1"/>
-    <col min="5" max="5" width="68.1083333333333" customWidth="1"/>
-    <col min="6" max="6" width="24.4416666666667" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="31.5583333333333" customWidth="1"/>
-    <col min="9" max="9" width="21.3333333333333" customWidth="1"/>
-    <col min="10" max="10" width="24.775" customWidth="1"/>
-    <col min="11" max="11" width="33.1083333333333" customWidth="1"/>
+    <col min="1" max="1" width="23" style="2" customWidth="1"/>
+    <col min="2" max="2" width="33.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="39.75" style="2" customWidth="1"/>
+    <col min="4" max="4" width="44" style="2" customWidth="1"/>
+    <col min="5" max="5" width="71.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="31" style="2" customWidth="1"/>
+    <col min="7" max="7" width="32.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="29" style="2" customWidth="1"/>
+    <col min="9" max="9" width="38.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="35.125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="26.75" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:11">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:11">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="57" spans="1:11">
-      <c r="A3" s="3" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:11">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" ht="86" customHeight="1" spans="5:5">
-      <c r="E4" s="4"/>
+    <row r="4" spans="2:8">
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="5" customFormat="1" ht="86" customHeight="1" spans="5:5">
-      <c r="E5" s="4"/>
+    <row r="5" spans="2:5">
+      <c r="B5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="B7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="B11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="3" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Excels/__tables__.xlsx
+++ b/Config/Excels/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="7305" windowHeight="7650"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -122,24 +122,6 @@
     <t>c</t>
   </si>
   <si>
-    <t>Tables.TbMap</t>
-  </si>
-  <si>
-    <t>MapConfig</t>
-  </si>
-  <si>
-    <t>.\Tables\Map_map.xlsx</t>
-  </si>
-  <si>
-    <t>Tables.TbModel</t>
-  </si>
-  <si>
-    <t>ModelConfig</t>
-  </si>
-  <si>
-    <t>.\Tables\Model_model.xlsx</t>
-  </si>
-  <si>
     <t>Tables.Global</t>
   </si>
   <si>
@@ -152,28 +134,25 @@
     <t>singleton</t>
   </si>
   <si>
-    <t>Tables.TbBadWords</t>
-  </si>
-  <si>
-    <t>BadWordsConfig</t>
-  </si>
-  <si>
-    <t>.\Tables\Words_BadWords.xlsx</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>Tables.TbNpc</t>
-  </si>
-  <si>
-    <t>NpcConfig</t>
-  </si>
-  <si>
-    <t>.\Tables\Npc_npc.xlsx</t>
-  </si>
-  <si>
-    <t>、</t>
+    <t>Tables.TbItem</t>
+  </si>
+  <si>
+    <t>ItemConfig</t>
+  </si>
+  <si>
+    <t>.\Tables\Item_item.xlsx</t>
+  </si>
+  <si>
+    <t>道具表</t>
+  </si>
+  <si>
+    <t>Tables.Shop</t>
+  </si>
+  <si>
+    <t>ShopConfig</t>
+  </si>
+  <si>
+    <t>.\Tables\Shop_shop.xlsx</t>
   </si>
 </sst>
 </file>
@@ -186,7 +165,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,13 +176,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -666,162 +638,159 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1143,8 +1112,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="23" style="2" customWidth="1"/>
     <col min="2" max="2" width="33.25" style="2" customWidth="1"/>
@@ -1157,7 +1126,7 @@
     <col min="9" max="9" width="38.25" style="2" customWidth="1"/>
     <col min="10" max="10" width="35.125" style="2" customWidth="1"/>
     <col min="11" max="11" width="26.75" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="12" max="16384" width="9" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:11">
@@ -1250,7 +1219,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="1:11">
       <c r="B4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1267,7 +1236,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" spans="1:11">
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
@@ -1280,78 +1249,45 @@
       <c r="E5" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="G5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="7" spans="2:5">
+    <row r="6" spans="1:11">
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5">
-      <c r="B11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
